--- a/temp_ResultOverview_allTests.xlsx
+++ b/temp_ResultOverview_allTests.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wu-my.sharepoint.com/personal/h12328919_s_wu_ac_at/Documents/Dokumente/Uni/Claude/BA/BA_Code/temp2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="241" documentId="8_{BFEB2E5B-F5F5-E246-BCB9-DAEC91FA11D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D58C3C75-2341-7F48-B05D-F7A177D14207}"/>
+  <xr:revisionPtr revIDLastSave="269" documentId="8_{BFEB2E5B-F5F5-E246-BCB9-DAEC91FA11D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A94E60E-886D-864F-A5E2-1EDA828E3D04}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="2160" windowWidth="51200" windowHeight="28800" xr2:uid="{91E8CCDD-4C2B-D24D-9CF8-DEDA9BB57E57}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26880" xr2:uid="{91E8CCDD-4C2B-D24D-9CF8-DEDA9BB57E57}"/>
   </bookViews>
   <sheets>
     <sheet name="ResultOverview_allTests" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -925,11 +938,6 @@
         <filter val="C"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="0"/>
-      </filters>
-    </filterColumn>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A13:AN17">
     <sortCondition ref="AM1:AM20"/>
@@ -2735,7 +2743,7 @@
         <v>0.61800377231739101</v>
       </c>
     </row>
-    <row r="15" spans="1:41" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>46180.852777777778</v>
       </c>
@@ -2857,7 +2865,7 @@
         <v>0.62599517636979896</v>
       </c>
     </row>
-    <row r="16" spans="1:41" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>46180.888194444444</v>
       </c>

--- a/temp_ResultOverview_allTests.xlsx
+++ b/temp_ResultOverview_allTests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wu-my.sharepoint.com/personal/h12328919_s_wu_ac_at/Documents/Dokumente/Uni/Claude/BA/BA_Code/temp2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="269" documentId="8_{BFEB2E5B-F5F5-E246-BCB9-DAEC91FA11D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A94E60E-886D-864F-A5E2-1EDA828E3D04}"/>
+  <xr:revisionPtr revIDLastSave="275" documentId="8_{BFEB2E5B-F5F5-E246-BCB9-DAEC91FA11D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A49E6530-6DC1-F84E-9257-88C46B825042}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26880" xr2:uid="{91E8CCDD-4C2B-D24D-9CF8-DEDA9BB57E57}"/>
+    <workbookView xWindow="-29400" yWindow="6580" windowWidth="29400" windowHeight="18480" xr2:uid="{91E8CCDD-4C2B-D24D-9CF8-DEDA9BB57E57}"/>
   </bookViews>
   <sheets>
     <sheet name="ResultOverview_allTests" sheetId="1" r:id="rId1"/>
@@ -846,12 +846,14 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -924,10 +926,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2608,13 +2606,13 @@
       <c r="AJ13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="AK13" s="3">
+      <c r="AK13" s="5">
         <v>0.54811715481171497</v>
       </c>
-      <c r="AL13" s="3">
+      <c r="AL13" s="5">
         <v>0.59519408502772597</v>
       </c>
-      <c r="AM13" s="3">
+      <c r="AM13" s="5">
         <v>0.67357512953367804</v>
       </c>
       <c r="AN13" s="3">
@@ -2730,13 +2728,13 @@
       <c r="AJ14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AK14" s="5">
         <v>0.57731958762886504</v>
       </c>
-      <c r="AL14" s="4">
+      <c r="AL14" s="6">
         <v>0.6</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AM14" s="5">
         <v>0.67669172932330801</v>
       </c>
       <c r="AN14" s="3">
@@ -2852,13 +2850,13 @@
       <c r="AJ15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AK15" s="5">
         <v>0.56491228070175403</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AL15" s="5">
         <v>0.63057324840764295</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AM15" s="5">
         <v>0.682499999999999</v>
       </c>
       <c r="AN15" s="3">
@@ -2974,13 +2972,13 @@
       <c r="AJ16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AK16" s="3">
+      <c r="AK16" s="5">
         <v>0.60759493670886</v>
       </c>
-      <c r="AL16" s="3">
+      <c r="AL16" s="5">
         <v>0.60702875399361</v>
       </c>
-      <c r="AM16" s="4">
+      <c r="AM16" s="6">
         <v>0.7</v>
       </c>
       <c r="AN16" s="3">
@@ -3096,13 +3094,13 @@
       <c r="AJ17" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AK17" s="5">
         <v>0.575809199318568</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AL17" s="5">
         <v>0.62046204620461998</v>
       </c>
-      <c r="AM17" s="4">
+      <c r="AM17" s="6">
         <v>0.701363073</v>
       </c>
       <c r="AN17" s="3">
